--- a/data.xlsx
+++ b/data.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBAC9B4D-A3B2-428E-8DA6-C56357C44BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C78C8A-9841-46A2-9456-2F43FB8FB5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="8" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="8" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Term-1" sheetId="4" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="310">
   <si>
     <t>#</t>
   </si>
@@ -3187,7 +3187,7 @@
                   <c:v>76509.399999999907</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-186485</c:v>
+                  <c:v>-201485</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3719,7 +3719,7 @@
                 <c:formatCode>"₹"\ #,##0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>4083767.4000000004</c:v>
+                  <c:v>4068767.4000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4134,7 +4134,7 @@
                   <c:v>3039754.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>30677.899999999907</c:v>
+                  <c:v>15677.899999999907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10574,15 +10574,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J38:K38"/>
     <mergeCell ref="B44:C44"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
@@ -10599,6 +10590,15 @@
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="J32:K32"/>
     <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J38:K38"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
@@ -11680,15 +11680,11 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
     <mergeCell ref="J38:K38"/>
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="H15:I15"/>
@@ -11700,11 +11696,15 @@
     <mergeCell ref="J35:K35"/>
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="J37:K37"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="22" priority="2" operator="greaterThan">
@@ -12935,15 +12935,11 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
     <mergeCell ref="J38:K38"/>
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="H15:I15"/>
@@ -12955,11 +12951,15 @@
     <mergeCell ref="J35:K35"/>
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="J37:K37"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="17" priority="3" operator="greaterThan">
@@ -14170,11 +14170,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
     <mergeCell ref="J38:K38"/>
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="H15:I15"/>
@@ -14186,15 +14190,11 @@
     <mergeCell ref="J35:K35"/>
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="J37:K37"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
@@ -14267,7 +14267,7 @@
       </c>
       <c r="K1" s="189">
         <f>M2-E2</f>
-        <v>-186485</v>
+        <v>-201485</v>
       </c>
       <c r="L1" s="190"/>
       <c r="M1" s="18"/>
@@ -14281,15 +14281,15 @@
       </c>
       <c r="E2" s="12">
         <f>SUM(E5:E30)</f>
-        <v>186485</v>
+        <v>201485</v>
       </c>
       <c r="F2" s="20"/>
       <c r="G2" s="31" t="s">
         <v>32</v>
       </c>
       <c r="H2" s="178" t="str">
-        <f ca="1">IF(ISBLANK(H1),"0 Days",CONCATENATE(_xlfn.DAYS(TODAY(), H1-1)," days"))</f>
-        <v>14 days</v>
+        <f ca="1">IF(ISBLANK(H1),"0 Days",CONCATENATE(_xlfn.DAYS(TODAY(), H1)," days"))</f>
+        <v>39 days</v>
       </c>
       <c r="I2" s="193"/>
       <c r="J2" s="37"/>
@@ -14457,9 +14457,15 @@
       <c r="B8" s="40">
         <v>4</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="5"/>
+      <c r="C8" s="7">
+        <v>46281</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="5">
+        <v>15000</v>
+      </c>
       <c r="F8" s="22"/>
       <c r="G8" s="43"/>
       <c r="H8" s="44"/>
@@ -14641,8 +14647,8 @@
         <v>32</v>
       </c>
       <c r="H16" s="178" t="str">
-        <f ca="1">IF(ISBLANK(H15),"0 Days",CONCATENATE(_xlfn.DAYS(TODAY(), H1-1)," days"))</f>
-        <v>14 days</v>
+        <f ca="1">IF(ISBLANK(H15),"0 Days",CONCATENATE(_xlfn.DAYS(TODAY(), H1)," days"))</f>
+        <v>39 days</v>
       </c>
       <c r="I16" s="179"/>
       <c r="J16" s="21">
@@ -15247,15 +15253,11 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
     <mergeCell ref="J38:K38"/>
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="H15:I15"/>
@@ -15267,11 +15269,15 @@
     <mergeCell ref="J35:K35"/>
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="J37:K37"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
@@ -15990,7 +15996,7 @@
       </c>
       <c r="D15" s="145">
         <f t="shared" ref="D15" si="6">IF(F15="","",E15-F15)</f>
-        <v>-186485</v>
+        <v>-201485</v>
       </c>
       <c r="E15" s="146">
         <f>'Term-14'!$M$2</f>
@@ -15998,7 +16004,7 @@
       </c>
       <c r="F15" s="146">
         <f>'Term-14'!$E$2</f>
-        <v>186485</v>
+        <v>201485</v>
       </c>
       <c r="G15" s="147">
         <f>MIN('Term-14'!H6:H14)</f>
@@ -16006,7 +16012,7 @@
       </c>
       <c r="H15" s="148" t="str" cm="1">
         <f t="array" aca="1" ref="H15:I15" ca="1">'Term-14'!H2:I2</f>
-        <v>14 days</v>
+        <v>39 days</v>
       </c>
       <c r="I15" s="149">
         <f ca="1"/>
@@ -16168,7 +16174,7 @@
       <c r="C25" s="204"/>
       <c r="D25" s="9">
         <f>SUM(D2:D24)</f>
-        <v>4083767.4000000004</v>
+        <v>4068767.4000000004</v>
       </c>
       <c r="E25" s="87">
         <f>SUM(E2:E24)</f>
@@ -16176,7 +16182,7 @@
       </c>
       <c r="F25" s="87">
         <f>SUM(F2:F24)</f>
-        <v>17034539</v>
+        <v>17049539</v>
       </c>
       <c r="G25" s="136"/>
       <c r="H25" s="87"/>
@@ -16264,7 +16270,7 @@
       </c>
       <c r="D32" s="87">
         <f>SUM(D12:D15)</f>
-        <v>30677.899999999907</v>
+        <v>15677.899999999907</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -16298,7 +16304,7 @@
       </c>
       <c r="D35" s="9">
         <f>SUM(D29:D34)</f>
-        <v>4083767.4</v>
+        <v>4068767.4</v>
       </c>
     </row>
   </sheetData>
@@ -16334,7 +16340,7 @@
       <c r="E1" s="206"/>
       <c r="F1" s="207" t="str">
         <f ca="1">DATEDIF(L1,TODAY(),"y")&amp;" year, "&amp;DATEDIF(L1,TODAY(),"ym")&amp;" months, "&amp;TODAY()-DATE(YEAR(TODAY()),MONTH(TODAY()),1)&amp;" days"</f>
-        <v>3 year, 4 months, 21 days</v>
+        <v>3 year, 5 months, 16 days</v>
       </c>
       <c r="G1" s="208"/>
       <c r="H1" s="208"/>
@@ -17536,12 +17542,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H13:I13"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -17550,6 +17550,12 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H13:I13"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D30">
     <cfRule type="duplicateValues" dxfId="68" priority="28"/>
@@ -19676,11 +19682,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="B3:F3"/>
@@ -19688,6 +19689,11 @@
     <mergeCell ref="J3:N3"/>
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="G14:I14"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="54" priority="4" operator="greaterThan">
@@ -22166,6 +22172,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="A43:C43"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -22174,11 +22185,6 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="46" priority="1" operator="greaterThan">
@@ -23450,6 +23456,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -23458,11 +23469,6 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="42" priority="2" operator="greaterThan">
@@ -24621,11 +24627,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -24634,6 +24635,11 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="37" priority="2" operator="greaterThan">
@@ -25800,23 +25806,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -25825,6 +25814,23 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="B43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="32" priority="2" operator="greaterThan">

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C78C8A-9841-46A2-9456-2F43FB8FB5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15984FF0-8368-49C5-838D-A59A943FC5D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="8" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,12 +22,13 @@
     <sheet name="Term-12" sheetId="19" r:id="rId12"/>
     <sheet name="Term-13" sheetId="20" r:id="rId13"/>
     <sheet name="Term-14" sheetId="21" r:id="rId14"/>
-    <sheet name="List" sheetId="12" r:id="rId15"/>
-    <sheet name="Summary Graph" sheetId="22" r:id="rId16"/>
-    <sheet name="Notes" sheetId="14" r:id="rId17"/>
+    <sheet name="Term-15" sheetId="23" r:id="rId15"/>
+    <sheet name="List" sheetId="12" r:id="rId16"/>
+    <sheet name="Summary Graph" sheetId="22" r:id="rId17"/>
+    <sheet name="Notes" sheetId="14" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">List!$B$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">List!$B$1:$L$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -67,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="313">
   <si>
     <t>#</t>
   </si>
@@ -942,9 +943,6 @@
     <t>Big Tank - First Middle - 119C-121R-2000T</t>
   </si>
   <si>
-    <t>Aug2026 - Oct2026</t>
-  </si>
-  <si>
     <t>Term-14</t>
   </si>
   <si>
@@ -997,6 +995,18 @@
   </si>
   <si>
     <t>Small Tank - Loose Shell</t>
+  </si>
+  <si>
+    <t>Aug2026 - Sept2026</t>
+  </si>
+  <si>
+    <t>Oct2026 - Dec2026</t>
+  </si>
+  <si>
+    <t>57 days</t>
+  </si>
+  <si>
+    <t>Big Tank Loose Shell</t>
   </si>
 </sst>
 </file>
@@ -2271,7 +2281,49 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="76">
+  <dxfs count="82">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3187,7 +3239,7 @@
                   <c:v>76509.399999999907</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-201485</c:v>
+                  <c:v>110337</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3719,7 +3771,7 @@
                 <c:formatCode>"₹"\ #,##0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>4068767.4000000004</c:v>
+                  <c:v>4380589.4000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4134,7 +4186,7 @@
                   <c:v>3039754.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>15677.899999999907</c:v>
+                  <c:v>327499.89999999991</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6447,6 +6499,107 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>96982</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F31D7556-7882-445F-9203-AA098A9BBBD9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="152400" y="8115300"/>
+          <a:ext cx="302722" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FAA9454-66BB-41C6-953E-DDD9272D08F2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="358140" y="8115300"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>226736</xdr:colOff>
       <xdr:row>1</xdr:row>
@@ -6667,7 +6820,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -9131,7 +9284,7 @@
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F33" s="57">
         <f>H33*G33</f>
@@ -9336,27 +9489,27 @@
     <mergeCell ref="H14:I14"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D30">
-    <cfRule type="duplicateValues" dxfId="75" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E30">
-    <cfRule type="duplicateValues" dxfId="74" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" dxfId="73" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="79" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="78" priority="7" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L30">
-    <cfRule type="duplicateValues" dxfId="71" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M30">
-    <cfRule type="duplicateValues" dxfId="70" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="S24:S26">
-    <cfRule type="duplicateValues" dxfId="69" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10574,6 +10727,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J38:K38"/>
     <mergeCell ref="B44:C44"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
@@ -10590,32 +10752,23 @@
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="J32:K32"/>
     <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J38:K38"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="32" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L6">
-    <cfRule type="duplicateValues" dxfId="25" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L7:L22">
-    <cfRule type="duplicateValues" dxfId="24" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M22">
-    <cfRule type="duplicateValues" dxfId="23" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -11680,11 +11833,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
     <mergeCell ref="J38:K38"/>
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="H15:I15"/>
@@ -11696,32 +11853,28 @@
     <mergeCell ref="J35:K35"/>
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="J37:K37"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" dxfId="22" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="28" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="27" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L6">
-    <cfRule type="duplicateValues" dxfId="20" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L7:L22">
-    <cfRule type="duplicateValues" dxfId="19" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M22">
-    <cfRule type="duplicateValues" dxfId="18" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -12923,6 +13076,1241 @@
       <c r="H45" s="107">
         <f>H43+H44</f>
         <v>1287593.9849624061</v>
+      </c>
+    </row>
+    <row r="54" spans="6:10" x14ac:dyDescent="0.3">
+      <c r="F54" s="39"/>
+    </row>
+    <row r="56" spans="6:10" x14ac:dyDescent="0.3">
+      <c r="J56" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+  </mergeCells>
+  <conditionalFormatting sqref="K1:L1">
+    <cfRule type="cellIs" dxfId="23" priority="3" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="4" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L5">
+    <cfRule type="duplicateValues" dxfId="21" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L6">
+    <cfRule type="duplicateValues" dxfId="20" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L7:L22">
+    <cfRule type="duplicateValues" dxfId="19" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M5:M22">
+    <cfRule type="duplicateValues" dxfId="18" priority="6"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;8&amp;K000000 INTERNAL USE</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDC6FD52-3033-4087-B599-2D13A03E21B7}">
+  <dimension ref="B1:N56"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.21875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="3" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" style="6" customWidth="1"/>
+    <col min="4" max="4" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="40" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.88671875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="22.5546875" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="186" t="s">
+        <v>282</v>
+      </c>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="188"/>
+      <c r="G1" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="176">
+        <v>46154</v>
+      </c>
+      <c r="I1" s="177"/>
+      <c r="J1" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="189">
+        <f>M2-E2</f>
+        <v>76509.399999999907</v>
+      </c>
+      <c r="L1" s="190"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="19"/>
+    </row>
+    <row r="2" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B2" s="191"/>
+      <c r="C2" s="192"/>
+      <c r="D2" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="12">
+        <f>SUM(E5:E30)</f>
+        <v>1439577</v>
+      </c>
+      <c r="F2" s="20"/>
+      <c r="G2" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" s="178" t="s">
+        <v>295</v>
+      </c>
+      <c r="I2" s="193"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="12">
+        <f>SUM(M5:M22)</f>
+        <v>1516086.4</v>
+      </c>
+      <c r="N2" s="20"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B3" s="194" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="195"/>
+      <c r="D3" s="196"/>
+      <c r="E3" s="196"/>
+      <c r="F3" s="197"/>
+      <c r="G3" s="180" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" s="181"/>
+      <c r="I3" s="181"/>
+      <c r="J3" s="194" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" s="195"/>
+      <c r="L3" s="196"/>
+      <c r="M3" s="196"/>
+      <c r="N3" s="197"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B4" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="99" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="99" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" s="22" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B5" s="40">
+        <v>1</v>
+      </c>
+      <c r="C5" s="7">
+        <v>46154</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="9">
+        <v>256000</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>279</v>
+      </c>
+      <c r="G5" s="43">
+        <v>46184</v>
+      </c>
+      <c r="H5" s="44">
+        <v>350</v>
+      </c>
+      <c r="I5" s="47" t="str">
+        <f>IF(ISBLANK(G5),"",CONCATENATE(G5-$H$1+1," days"))</f>
+        <v>31 days</v>
+      </c>
+      <c r="J5" s="21">
+        <v>1</v>
+      </c>
+      <c r="K5" s="43">
+        <v>46214</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="M5" s="5">
+        <v>388886.4</v>
+      </c>
+      <c r="N5" s="22"/>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B6" s="40">
+        <v>2</v>
+      </c>
+      <c r="C6" s="7">
+        <v>46154</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" s="5">
+        <v>15000</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>280</v>
+      </c>
+      <c r="G6" s="43">
+        <v>46207</v>
+      </c>
+      <c r="H6" s="44">
+        <v>150</v>
+      </c>
+      <c r="I6" s="47" t="str">
+        <f t="shared" ref="I6:I13" si="0">IF(ISBLANK(G6),"",CONCATENATE(G6-$H$1+1," days"))</f>
+        <v>54 days</v>
+      </c>
+      <c r="J6" s="21">
+        <v>2</v>
+      </c>
+      <c r="K6" s="46">
+        <v>46222</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="M6" s="5">
+        <v>955200</v>
+      </c>
+      <c r="N6" s="22"/>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B7" s="40">
+        <v>3</v>
+      </c>
+      <c r="C7" s="7">
+        <v>46152</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="E7" s="5">
+        <v>10000</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>284</v>
+      </c>
+      <c r="G7" s="43">
+        <v>46212</v>
+      </c>
+      <c r="H7" s="44">
+        <v>125</v>
+      </c>
+      <c r="I7" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>59 days</v>
+      </c>
+      <c r="J7" s="21">
+        <v>3</v>
+      </c>
+      <c r="K7" s="46">
+        <v>46222</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="M7" s="5">
+        <v>172000</v>
+      </c>
+      <c r="N7" s="22"/>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B8" s="40">
+        <v>4</v>
+      </c>
+      <c r="C8" s="7">
+        <v>46161</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="5">
+        <v>14953</v>
+      </c>
+      <c r="F8" s="22"/>
+      <c r="G8" s="43">
+        <v>46214</v>
+      </c>
+      <c r="H8" s="44">
+        <v>119</v>
+      </c>
+      <c r="I8" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>61 days</v>
+      </c>
+      <c r="J8" s="21">
+        <v>4</v>
+      </c>
+      <c r="K8" s="4"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="22"/>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B9" s="40">
+        <v>5</v>
+      </c>
+      <c r="C9" s="127">
+        <v>46167</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E9" s="9">
+        <v>3000</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="46">
+        <v>46221</v>
+      </c>
+      <c r="H9" s="44">
+        <v>100</v>
+      </c>
+      <c r="I9" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>68 days</v>
+      </c>
+      <c r="J9" s="21">
+        <v>5</v>
+      </c>
+      <c r="K9" s="4"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="22"/>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B10" s="40">
+        <v>6</v>
+      </c>
+      <c r="C10" s="127">
+        <v>46191</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="9">
+        <v>1039463</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>306</v>
+      </c>
+      <c r="G10" s="46">
+        <v>46222</v>
+      </c>
+      <c r="H10" s="44">
+        <v>95</v>
+      </c>
+      <c r="I10" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>69 days</v>
+      </c>
+      <c r="J10" s="21">
+        <v>6</v>
+      </c>
+      <c r="K10" s="2"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="22"/>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B11" s="40">
+        <v>7</v>
+      </c>
+      <c r="C11" s="127">
+        <v>46181</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="5">
+        <v>12238</v>
+      </c>
+      <c r="F11" s="22"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J11" s="21">
+        <v>7</v>
+      </c>
+      <c r="K11" s="2"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="22"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B12" s="40">
+        <v>8</v>
+      </c>
+      <c r="C12" s="7">
+        <v>46190</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E12" s="5">
+        <v>8000</v>
+      </c>
+      <c r="F12" s="55"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="109"/>
+      <c r="I12" s="121" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J12" s="40">
+        <v>8</v>
+      </c>
+      <c r="K12" s="2"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="22"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B13" s="40">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>46221</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="5">
+        <v>23923</v>
+      </c>
+      <c r="F13" s="55"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="109"/>
+      <c r="I13" s="121" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J13" s="40">
+        <v>9</v>
+      </c>
+      <c r="K13" s="2"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="22"/>
+    </row>
+    <row r="14" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="40">
+        <v>10</v>
+      </c>
+      <c r="C14" s="127">
+        <v>46222</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E14" s="9">
+        <v>25000</v>
+      </c>
+      <c r="F14" s="67"/>
+      <c r="G14" s="173" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14" s="174"/>
+      <c r="I14" s="175"/>
+      <c r="J14" s="21">
+        <v>10</v>
+      </c>
+      <c r="K14" s="2"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="22"/>
+    </row>
+    <row r="15" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="40">
+        <v>11</v>
+      </c>
+      <c r="C15" s="127">
+        <v>46222</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" s="5">
+        <v>32000</v>
+      </c>
+      <c r="F15" s="22"/>
+      <c r="G15" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="176">
+        <v>46154</v>
+      </c>
+      <c r="I15" s="177"/>
+      <c r="J15" s="21">
+        <v>11</v>
+      </c>
+      <c r="K15" s="2"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="22"/>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B16" s="40">
+        <v>12</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" s="178" t="s">
+        <v>295</v>
+      </c>
+      <c r="I16" s="179"/>
+      <c r="J16" s="21">
+        <v>12</v>
+      </c>
+      <c r="K16" s="2"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="22"/>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B17" s="40">
+        <v>13</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="180" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="181"/>
+      <c r="I17" s="182"/>
+      <c r="J17" s="21">
+        <v>13</v>
+      </c>
+      <c r="K17" s="2"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="22"/>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B18" s="40">
+        <v>14</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J18" s="40">
+        <v>14</v>
+      </c>
+      <c r="K18" s="2"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="22"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B19" s="40">
+        <v>15</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="43">
+        <v>46184</v>
+      </c>
+      <c r="H19" s="44">
+        <v>350</v>
+      </c>
+      <c r="I19" s="47" t="str">
+        <f>IF(ISBLANK(G19),"",CONCATENATE(G19-$H$15+1," days"))</f>
+        <v>31 days</v>
+      </c>
+      <c r="J19" s="21">
+        <v>15</v>
+      </c>
+      <c r="K19" s="2"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="22"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B20" s="40">
+        <v>16</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="43">
+        <v>46221</v>
+      </c>
+      <c r="H20" s="44">
+        <v>90</v>
+      </c>
+      <c r="I20" s="47" t="str">
+        <f t="shared" ref="I20:I25" si="1">IF(ISBLANK(G20),"",CONCATENATE(G20-$H$15+1," days"))</f>
+        <v>68 days</v>
+      </c>
+      <c r="J20" s="21">
+        <v>16</v>
+      </c>
+      <c r="K20" s="2"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="22"/>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B21" s="40">
+        <v>17</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="46">
+        <v>46222</v>
+      </c>
+      <c r="H21" s="44">
+        <v>90</v>
+      </c>
+      <c r="I21" s="47" t="str">
+        <f t="shared" si="1"/>
+        <v>69 days</v>
+      </c>
+      <c r="J21" s="21">
+        <v>17</v>
+      </c>
+      <c r="K21" s="2"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="22"/>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B22" s="40">
+        <v>18</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="47" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J22" s="21">
+        <v>18</v>
+      </c>
+      <c r="K22" s="2"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="22"/>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B23" s="40">
+        <v>19</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="47" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J23" s="21">
+        <v>19</v>
+      </c>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="33"/>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B24" s="40">
+        <v>20</v>
+      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="47" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J24" s="21">
+        <v>20</v>
+      </c>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="33"/>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B25" s="40">
+        <v>21</v>
+      </c>
+      <c r="C25" s="4"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="47" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J25" s="21">
+        <v>21</v>
+      </c>
+      <c r="K25" s="15"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="33"/>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B26" s="40">
+        <v>22</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="47"/>
+      <c r="J26" s="21">
+        <v>22</v>
+      </c>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="33"/>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B27" s="40">
+        <v>23</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="47"/>
+      <c r="J27" s="21">
+        <v>23</v>
+      </c>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="33"/>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B28" s="40">
+        <v>24</v>
+      </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="21">
+        <v>24</v>
+      </c>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="33"/>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B29" s="40">
+        <v>25</v>
+      </c>
+      <c r="C29" s="69"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="72"/>
+      <c r="G29" s="73"/>
+      <c r="H29" s="74"/>
+      <c r="I29" s="75"/>
+      <c r="J29" s="21">
+        <v>25</v>
+      </c>
+      <c r="K29" s="68"/>
+      <c r="L29" s="68"/>
+      <c r="M29" s="68"/>
+      <c r="N29" s="76"/>
+    </row>
+    <row r="30" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="77"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="61"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="49"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="38"/>
+      <c r="L30" s="68"/>
+      <c r="M30" s="68"/>
+      <c r="N30" s="76"/>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B31" s="24"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="F31" s="84">
+        <f>H31+J31</f>
+        <v>800000</v>
+      </c>
+      <c r="G31" s="90" t="s">
+        <v>186</v>
+      </c>
+      <c r="H31" s="84">
+        <v>700000</v>
+      </c>
+      <c r="I31" s="59" t="s">
+        <v>187</v>
+      </c>
+      <c r="J31" s="84">
+        <v>100000</v>
+      </c>
+      <c r="K31" s="84"/>
+      <c r="L31" s="96"/>
+      <c r="M31" s="130"/>
+      <c r="N31" s="15"/>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="E32" s="59" t="s">
+        <v>62</v>
+      </c>
+      <c r="F32" s="90" t="s">
+        <v>54</v>
+      </c>
+      <c r="G32" s="90" t="s">
+        <v>26</v>
+      </c>
+      <c r="H32" s="90" t="s">
+        <v>95</v>
+      </c>
+      <c r="I32" s="90" t="s">
+        <v>63</v>
+      </c>
+      <c r="J32" s="183" t="s">
+        <v>64</v>
+      </c>
+      <c r="K32" s="183"/>
+      <c r="L32" s="184" t="s">
+        <v>158</v>
+      </c>
+      <c r="M32" s="185"/>
+      <c r="N32" s="15"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="E33" s="15" t="s">
+        <v>301</v>
+      </c>
+      <c r="F33" s="57">
+        <f>H33*G33</f>
+        <v>214247.6</v>
+      </c>
+      <c r="G33" s="57">
+        <v>119</v>
+      </c>
+      <c r="H33" s="65">
+        <v>1800.4</v>
+      </c>
+      <c r="I33" s="60">
+        <v>216</v>
+      </c>
+      <c r="J33" s="169">
+        <f>H33*I33</f>
+        <v>388886.4</v>
+      </c>
+      <c r="K33" s="169"/>
+      <c r="L33" s="83" t="s">
+        <v>60</v>
+      </c>
+      <c r="M33" s="131">
+        <v>1039463</v>
+      </c>
+      <c r="N33" s="15"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="E34" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="F34" s="57">
+        <f t="shared" ref="F34:F39" si="2">H34*G34</f>
+        <v>373730</v>
+      </c>
+      <c r="G34" s="57">
+        <v>95</v>
+      </c>
+      <c r="H34" s="65">
+        <v>3934</v>
+      </c>
+      <c r="I34" s="60">
+        <v>245</v>
+      </c>
+      <c r="J34" s="169">
+        <f t="shared" ref="J34:J39" si="3">H34*I34</f>
+        <v>963830</v>
+      </c>
+      <c r="K34" s="169"/>
+      <c r="L34" s="83" t="s">
+        <v>127</v>
+      </c>
+      <c r="M34" s="131">
+        <v>800000</v>
+      </c>
+      <c r="N34" s="15"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C35" s="122"/>
+      <c r="E35" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="F35" s="57">
+        <f t="shared" si="2"/>
+        <v>3600</v>
+      </c>
+      <c r="G35" s="57">
+        <v>90</v>
+      </c>
+      <c r="H35" s="65">
+        <v>40</v>
+      </c>
+      <c r="I35" s="60">
+        <v>60</v>
+      </c>
+      <c r="J35" s="169">
+        <f t="shared" si="3"/>
+        <v>2400</v>
+      </c>
+      <c r="K35" s="169"/>
+      <c r="L35" s="83"/>
+      <c r="M35" s="131"/>
+      <c r="N35" s="15" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="36" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="E36" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="F36" s="57">
+        <f t="shared" si="2"/>
+        <v>60723.000000000007</v>
+      </c>
+      <c r="G36" s="57">
+        <v>90</v>
+      </c>
+      <c r="H36" s="65">
+        <v>674.7</v>
+      </c>
+      <c r="I36" s="60">
+        <v>255</v>
+      </c>
+      <c r="J36" s="169">
+        <f t="shared" si="3"/>
+        <v>172048.5</v>
+      </c>
+      <c r="K36" s="169"/>
+      <c r="L36" s="83"/>
+      <c r="M36" s="131"/>
+      <c r="N36" s="15"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="E37" s="15" t="s">
+        <v>308</v>
+      </c>
+      <c r="F37" s="57">
+        <f t="shared" si="2"/>
+        <v>1260</v>
+      </c>
+      <c r="G37" s="57">
+        <v>90</v>
+      </c>
+      <c r="H37" s="65">
+        <v>14</v>
+      </c>
+      <c r="I37" s="60">
+        <v>60</v>
+      </c>
+      <c r="J37" s="169">
+        <f t="shared" si="3"/>
+        <v>840</v>
+      </c>
+      <c r="K37" s="169"/>
+      <c r="L37" s="83"/>
+      <c r="M37" s="131"/>
+      <c r="N37" s="15"/>
+    </row>
+    <row r="38" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="E38" s="15"/>
+      <c r="F38" s="57">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G38" s="57"/>
+      <c r="H38" s="65"/>
+      <c r="I38" s="60"/>
+      <c r="J38" s="169">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K38" s="169"/>
+      <c r="L38" s="83"/>
+      <c r="M38" s="131"/>
+      <c r="N38" s="15"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="E39" s="15"/>
+      <c r="F39" s="57">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G39" s="57"/>
+      <c r="H39" s="65"/>
+      <c r="I39" s="60"/>
+      <c r="J39" s="169">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="169"/>
+      <c r="L39" s="83"/>
+      <c r="M39" s="131"/>
+      <c r="N39" s="15"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="E40" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="F40" s="58">
+        <f>SUM(F33:F38)</f>
+        <v>653560.6</v>
+      </c>
+      <c r="G40" s="58"/>
+      <c r="H40" s="82">
+        <f>SUM(H33:H39)</f>
+        <v>6463.0999999999995</v>
+      </c>
+      <c r="I40" s="50"/>
+      <c r="J40" s="170">
+        <f>SUM(J33:J39)</f>
+        <v>1528004.9</v>
+      </c>
+      <c r="K40" s="170"/>
+      <c r="L40" s="50" t="s">
+        <v>88</v>
+      </c>
+      <c r="M40" s="132">
+        <f>SUM(M33:M39)</f>
+        <v>1839463</v>
+      </c>
+      <c r="N40" s="15"/>
+    </row>
+    <row r="41" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E41" s="50" t="s">
+        <v>126</v>
+      </c>
+      <c r="F41" s="105" t="str">
+        <f>CONCATENATE(ROUND((F40/F31)*100,2),"%")</f>
+        <v>81.7%</v>
+      </c>
+      <c r="G41" s="15"/>
+      <c r="H41" s="56"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="171"/>
+      <c r="K41" s="171"/>
+      <c r="L41" s="81" t="s">
+        <v>89</v>
+      </c>
+      <c r="M41" s="101">
+        <f>J40-M40</f>
+        <v>-311458.10000000009</v>
+      </c>
+      <c r="N41" s="15"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="D42" s="39"/>
+      <c r="L42" s="66"/>
+      <c r="M42" s="39"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B43" s="172" t="s">
+        <v>200</v>
+      </c>
+      <c r="C43" s="172"/>
+      <c r="D43" s="57">
+        <f>F31-F40</f>
+        <v>146439.40000000002</v>
+      </c>
+      <c r="E43" s="15">
+        <v>95</v>
+      </c>
+      <c r="F43" s="126">
+        <f>D43/E43</f>
+        <v>1541.4673684210529</v>
+      </c>
+      <c r="G43" s="60">
+        <v>240</v>
+      </c>
+      <c r="H43" s="97">
+        <f>F43*G43</f>
+        <v>369952.16842105269</v>
+      </c>
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="15"/>
+      <c r="M43" s="15"/>
+      <c r="N43" s="15"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B44" s="172" t="s">
+        <v>200</v>
+      </c>
+      <c r="C44" s="172"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="126" t="e">
+        <f>D44/E44</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G44" s="60"/>
+      <c r="H44" s="97" t="e">
+        <f>F44*G44</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I44" s="15"/>
+      <c r="J44" s="15"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="15"/>
+      <c r="M44" s="15"/>
+      <c r="N44" s="15"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="H45" s="107" t="e">
+        <f>H43+H44</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="54" spans="6:10" x14ac:dyDescent="0.3">
@@ -12990,8 +14378,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDC6FD52-3033-4087-B599-2D13A03E21B7}">
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25ED0D34-371C-44C4-8709-6060745CC3BB}">
   <dimension ref="B1:N56"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -13001,11 +14389,11 @@
     <col min="4" max="4" width="14" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.77734375" style="1" customWidth="1"/>
     <col min="10" max="10" width="8.33203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="40" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15.88671875" style="1" customWidth="1"/>
     <col min="14" max="14" width="22.5546875" style="1" customWidth="1"/>
@@ -13014,7 +14402,7 @@
   <sheetData>
     <row r="1" spans="2:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="186" t="s">
-        <v>282</v>
+        <v>309</v>
       </c>
       <c r="C1" s="187"/>
       <c r="D1" s="187"/>
@@ -13024,7 +14412,7 @@
         <v>25</v>
       </c>
       <c r="H1" s="176">
-        <v>46154</v>
+        <v>46243</v>
       </c>
       <c r="I1" s="177"/>
       <c r="J1" s="17" t="s">
@@ -13032,7 +14420,7 @@
       </c>
       <c r="K1" s="189">
         <f>M2-E2</f>
-        <v>76509.399999999907</v>
+        <v>110337</v>
       </c>
       <c r="L1" s="190"/>
       <c r="M1" s="18"/>
@@ -13046,14 +14434,14 @@
       </c>
       <c r="E2" s="12">
         <f>SUM(E5:E30)</f>
-        <v>1439577</v>
+        <v>651485</v>
       </c>
       <c r="F2" s="20"/>
       <c r="G2" s="31" t="s">
         <v>32</v>
       </c>
       <c r="H2" s="178" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="I2" s="193"/>
       <c r="J2" s="37"/>
@@ -13063,7 +14451,7 @@
       </c>
       <c r="M2" s="12">
         <f>SUM(M5:M22)</f>
-        <v>1516086.4</v>
+        <v>761822</v>
       </c>
       <c r="N2" s="20"/>
     </row>
@@ -13134,38 +14522,38 @@
         <v>1</v>
       </c>
       <c r="C5" s="7">
-        <v>46154</v>
+        <v>46243</v>
       </c>
       <c r="D5" s="26" t="s">
         <v>19</v>
       </c>
       <c r="E5" s="9">
-        <v>256000</v>
+        <v>165000</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>279</v>
+        <v>304</v>
       </c>
       <c r="G5" s="43">
-        <v>46184</v>
+        <v>46297</v>
       </c>
       <c r="H5" s="44">
-        <v>350</v>
+        <v>130</v>
       </c>
       <c r="I5" s="47" t="str">
         <f>IF(ISBLANK(G5),"",CONCATENATE(G5-$H$1+1," days"))</f>
-        <v>31 days</v>
+        <v>55 days</v>
       </c>
       <c r="J5" s="21">
         <v>1</v>
       </c>
       <c r="K5" s="43">
-        <v>46214</v>
+        <v>46299</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>290</v>
+        <v>116</v>
       </c>
       <c r="M5" s="5">
-        <v>388886.4</v>
+        <v>693462</v>
       </c>
       <c r="N5" s="22"/>
     </row>
@@ -13174,38 +14562,38 @@
         <v>2</v>
       </c>
       <c r="C6" s="7">
-        <v>46154</v>
+        <v>46243</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="E6" s="5">
-        <v>15000</v>
+        <v>5000</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G6" s="43">
-        <v>46207</v>
+        <v>46299</v>
       </c>
       <c r="H6" s="44">
-        <v>150</v>
+        <v>116</v>
       </c>
       <c r="I6" s="47" t="str">
         <f t="shared" ref="I6:I13" si="0">IF(ISBLANK(G6),"",CONCATENATE(G6-$H$1+1," days"))</f>
-        <v>54 days</v>
+        <v>57 days</v>
       </c>
       <c r="J6" s="21">
         <v>2</v>
       </c>
-      <c r="K6" s="46">
-        <v>46222</v>
+      <c r="K6" s="43">
+        <v>46299</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>295</v>
+        <v>143</v>
       </c>
       <c r="M6" s="5">
-        <v>955200</v>
+        <v>65600</v>
       </c>
       <c r="N6" s="22"/>
     </row>
@@ -13214,38 +14602,32 @@
         <v>3</v>
       </c>
       <c r="C7" s="7">
-        <v>46152</v>
+        <v>46249</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>283</v>
+        <v>29</v>
       </c>
       <c r="E7" s="5">
-        <v>10000</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>284</v>
-      </c>
-      <c r="G7" s="43">
-        <v>46212</v>
-      </c>
-      <c r="H7" s="44">
-        <v>125</v>
-      </c>
+        <v>16485</v>
+      </c>
+      <c r="F7" s="23"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="44"/>
       <c r="I7" s="47" t="str">
         <f t="shared" si="0"/>
-        <v>59 days</v>
+        <v/>
       </c>
       <c r="J7" s="21">
         <v>3</v>
       </c>
-      <c r="K7" s="46">
-        <v>46222</v>
+      <c r="K7" s="43">
+        <v>46299</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="M7" s="5">
-        <v>172000</v>
+        <v>2760</v>
       </c>
       <c r="N7" s="22"/>
     </row>
@@ -13254,24 +14636,20 @@
         <v>4</v>
       </c>
       <c r="C8" s="7">
-        <v>46161</v>
+        <v>46281</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>29</v>
       </c>
       <c r="E8" s="5">
-        <v>14953</v>
+        <v>15000</v>
       </c>
       <c r="F8" s="22"/>
-      <c r="G8" s="43">
-        <v>46214</v>
-      </c>
-      <c r="H8" s="44">
-        <v>119</v>
-      </c>
+      <c r="G8" s="43"/>
+      <c r="H8" s="44"/>
       <c r="I8" s="47" t="str">
         <f t="shared" si="0"/>
-        <v>61 days</v>
+        <v/>
       </c>
       <c r="J8" s="21">
         <v>4</v>
@@ -13285,27 +14663,21 @@
       <c r="B9" s="40">
         <v>5</v>
       </c>
-      <c r="C9" s="127">
-        <v>46167</v>
+      <c r="C9" s="43">
+        <v>46299</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>285</v>
+        <v>60</v>
       </c>
       <c r="E9" s="9">
-        <v>3000</v>
-      </c>
-      <c r="F9" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9" s="46">
-        <v>46221</v>
-      </c>
-      <c r="H9" s="44">
-        <v>100</v>
-      </c>
+        <v>450000</v>
+      </c>
+      <c r="F9" s="22"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="44"/>
       <c r="I9" s="47" t="str">
         <f t="shared" si="0"/>
-        <v>68 days</v>
+        <v/>
       </c>
       <c r="J9" s="21">
         <v>5</v>
@@ -13319,27 +14691,15 @@
       <c r="B10" s="40">
         <v>6</v>
       </c>
-      <c r="C10" s="127">
-        <v>46191</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="9">
-        <v>1039463</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>307</v>
-      </c>
-      <c r="G10" s="46">
-        <v>46222</v>
-      </c>
-      <c r="H10" s="44">
-        <v>95</v>
-      </c>
+      <c r="C10" s="127"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="44"/>
       <c r="I10" s="47" t="str">
         <f t="shared" si="0"/>
-        <v>69 days</v>
+        <v/>
       </c>
       <c r="J10" s="21">
         <v>6</v>
@@ -13353,15 +14713,9 @@
       <c r="B11" s="40">
         <v>7</v>
       </c>
-      <c r="C11" s="127">
-        <v>46181</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="5">
-        <v>12238</v>
-      </c>
+      <c r="C11" s="127"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="5"/>
       <c r="F11" s="22"/>
       <c r="G11" s="46"/>
       <c r="H11" s="44"/>
@@ -13381,15 +14735,9 @@
       <c r="B12" s="40">
         <v>8</v>
       </c>
-      <c r="C12" s="7">
-        <v>46190</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="E12" s="5">
-        <v>8000</v>
-      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="5"/>
       <c r="F12" s="55"/>
       <c r="G12" s="46"/>
       <c r="H12" s="109"/>
@@ -13409,15 +14757,9 @@
       <c r="B13" s="40">
         <v>9</v>
       </c>
-      <c r="C13" s="7">
-        <v>46221</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="5">
-        <v>23923</v>
-      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="5"/>
       <c r="F13" s="55"/>
       <c r="G13" s="46"/>
       <c r="H13" s="109"/>
@@ -13437,15 +14779,9 @@
       <c r="B14" s="40">
         <v>10</v>
       </c>
-      <c r="C14" s="127">
-        <v>46222</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="E14" s="9">
-        <v>25000</v>
-      </c>
+      <c r="C14" s="127"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="9"/>
       <c r="F14" s="67"/>
       <c r="G14" s="173" t="s">
         <v>57</v>
@@ -13464,21 +14800,15 @@
       <c r="B15" s="40">
         <v>11</v>
       </c>
-      <c r="C15" s="127">
-        <v>46222</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E15" s="5">
-        <v>32000</v>
-      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="5"/>
       <c r="F15" s="22"/>
       <c r="G15" s="16" t="s">
         <v>25</v>
       </c>
       <c r="H15" s="176">
-        <v>46154</v>
+        <v>46243</v>
       </c>
       <c r="I15" s="177"/>
       <c r="J15" s="21">
@@ -13501,7 +14831,7 @@
         <v>32</v>
       </c>
       <c r="H16" s="178" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="I16" s="179"/>
       <c r="J16" s="21">
@@ -13567,14 +14897,12 @@
       <c r="E19" s="5"/>
       <c r="F19" s="22"/>
       <c r="G19" s="43">
-        <v>46184</v>
-      </c>
-      <c r="H19" s="44">
-        <v>350</v>
-      </c>
+        <v>46299</v>
+      </c>
+      <c r="H19" s="44"/>
       <c r="I19" s="47" t="str">
         <f>IF(ISBLANK(G19),"",CONCATENATE(G19-$H$15+1," days"))</f>
-        <v>31 days</v>
+        <v>57 days</v>
       </c>
       <c r="J19" s="21">
         <v>15</v>
@@ -13592,15 +14920,11 @@
       <c r="D20" s="3"/>
       <c r="E20" s="5"/>
       <c r="F20" s="22"/>
-      <c r="G20" s="43">
-        <v>46221</v>
-      </c>
-      <c r="H20" s="44">
-        <v>90</v>
-      </c>
+      <c r="G20" s="43"/>
+      <c r="H20" s="44"/>
       <c r="I20" s="47" t="str">
         <f t="shared" ref="I20:I25" si="1">IF(ISBLANK(G20),"",CONCATENATE(G20-$H$15+1," days"))</f>
-        <v>68 days</v>
+        <v/>
       </c>
       <c r="J20" s="21">
         <v>16</v>
@@ -13618,15 +14942,11 @@
       <c r="D21" s="3"/>
       <c r="E21" s="5"/>
       <c r="F21" s="22"/>
-      <c r="G21" s="46">
-        <v>46222</v>
-      </c>
-      <c r="H21" s="44">
-        <v>90</v>
-      </c>
+      <c r="G21" s="46"/>
+      <c r="H21" s="44"/>
       <c r="I21" s="47" t="str">
         <f t="shared" si="1"/>
-        <v>69 days</v>
+        <v/>
       </c>
       <c r="J21" s="21">
         <v>17</v>
@@ -13824,13 +15144,13 @@
       </c>
       <c r="F31" s="84">
         <f>H31+J31</f>
-        <v>800000</v>
+        <v>550000</v>
       </c>
       <c r="G31" s="90" t="s">
         <v>186</v>
       </c>
       <c r="H31" s="84">
-        <v>700000</v>
+        <v>450000</v>
       </c>
       <c r="I31" s="59" t="s">
         <v>187</v>
@@ -13871,85 +15191,77 @@
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
-        <v>302</v>
+        <v>116</v>
       </c>
       <c r="F33" s="57">
         <f>H33*G33</f>
-        <v>214247.6</v>
+        <v>297198</v>
       </c>
       <c r="G33" s="57">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="H33" s="65">
-        <v>1800.4</v>
+        <v>2607</v>
       </c>
       <c r="I33" s="60">
-        <v>216</v>
+        <v>266</v>
       </c>
       <c r="J33" s="169">
         <f>H33*I33</f>
-        <v>388886.4</v>
+        <v>693462</v>
       </c>
       <c r="K33" s="169"/>
       <c r="L33" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="M33" s="131">
-        <v>1039463</v>
-      </c>
+      <c r="M33" s="131"/>
       <c r="N33" s="15"/>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.3">
       <c r="E34" s="15" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="F34" s="57">
         <f t="shared" ref="F34:F39" si="2">H34*G34</f>
-        <v>373730</v>
+        <v>46400</v>
       </c>
       <c r="G34" s="57">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="H34" s="65">
-        <v>3934</v>
+        <v>400</v>
       </c>
       <c r="I34" s="60">
-        <v>245</v>
+        <v>164</v>
       </c>
       <c r="J34" s="169">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
-        <v>963830</v>
+        <v>65600</v>
       </c>
       <c r="K34" s="169"/>
-      <c r="L34" s="83" t="s">
-        <v>127</v>
-      </c>
-      <c r="M34" s="131">
-        <v>800000</v>
-      </c>
+      <c r="L34" s="83"/>
+      <c r="M34" s="131"/>
       <c r="N34" s="15"/>
     </row>
     <row r="35" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C35" s="122"/>
-      <c r="E35" s="15" t="s">
-        <v>308</v>
-      </c>
+      <c r="E35" s="15"/>
       <c r="F35" s="57">
         <f t="shared" si="2"/>
-        <v>3600</v>
+        <v>5244</v>
       </c>
       <c r="G35" s="57">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="H35" s="65">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I35" s="60">
         <v>60</v>
       </c>
       <c r="J35" s="169">
         <f t="shared" si="3"/>
-        <v>2400</v>
+        <v>2760</v>
       </c>
       <c r="K35" s="169"/>
       <c r="L35" s="83"/>
@@ -13959,25 +15271,17 @@
       </c>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="E36" s="15" t="s">
-        <v>224</v>
-      </c>
+      <c r="E36" s="15"/>
       <c r="F36" s="57">
         <f t="shared" si="2"/>
-        <v>60723.000000000007</v>
-      </c>
-      <c r="G36" s="57">
-        <v>90</v>
-      </c>
-      <c r="H36" s="65">
-        <v>674.7</v>
-      </c>
-      <c r="I36" s="60">
-        <v>255</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G36" s="57"/>
+      <c r="H36" s="65"/>
+      <c r="I36" s="60"/>
       <c r="J36" s="169">
         <f t="shared" si="3"/>
-        <v>172048.5</v>
+        <v>0</v>
       </c>
       <c r="K36" s="169"/>
       <c r="L36" s="83"/>
@@ -13985,25 +15289,17 @@
       <c r="N36" s="15"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="E37" s="15" t="s">
-        <v>309</v>
-      </c>
+      <c r="E37" s="15"/>
       <c r="F37" s="57">
         <f t="shared" si="2"/>
-        <v>1260</v>
-      </c>
-      <c r="G37" s="57">
-        <v>90</v>
-      </c>
-      <c r="H37" s="65">
-        <v>14</v>
-      </c>
-      <c r="I37" s="60">
-        <v>60</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G37" s="57"/>
+      <c r="H37" s="65"/>
+      <c r="I37" s="60"/>
       <c r="J37" s="169">
         <f t="shared" si="3"/>
-        <v>840</v>
+        <v>0</v>
       </c>
       <c r="K37" s="169"/>
       <c r="L37" s="83"/>
@@ -14052,17 +15348,17 @@
       </c>
       <c r="F40" s="58">
         <f>SUM(F33:F38)</f>
-        <v>653560.6</v>
+        <v>348842</v>
       </c>
       <c r="G40" s="58"/>
       <c r="H40" s="82">
         <f>SUM(H33:H39)</f>
-        <v>6463.0999999999995</v>
+        <v>3053</v>
       </c>
       <c r="I40" s="50"/>
       <c r="J40" s="170">
         <f>SUM(J33:J39)</f>
-        <v>1528004.9</v>
+        <v>761822</v>
       </c>
       <c r="K40" s="170"/>
       <c r="L40" s="50" t="s">
@@ -14070,7 +15366,7 @@
       </c>
       <c r="M40" s="132">
         <f>SUM(M33:M39)</f>
-        <v>1839463</v>
+        <v>0</v>
       </c>
       <c r="N40" s="15"/>
     </row>
@@ -14080,7 +15376,7 @@
       </c>
       <c r="F41" s="105" t="str">
         <f>CONCATENATE(ROUND((F40/F31)*100,2),"%")</f>
-        <v>81.7%</v>
+        <v>63.43%</v>
       </c>
       <c r="G41" s="15"/>
       <c r="H41" s="56"/>
@@ -14092,7 +15388,7 @@
       </c>
       <c r="M41" s="101">
         <f>J40-M40</f>
-        <v>-311458.10000000009</v>
+        <v>761822</v>
       </c>
       <c r="N41" s="15"/>
     </row>
@@ -14106,23 +15402,16 @@
         <v>200</v>
       </c>
       <c r="C43" s="172"/>
-      <c r="D43" s="57">
-        <f>F31-F40</f>
-        <v>146439.40000000002</v>
-      </c>
-      <c r="E43" s="15">
-        <v>95</v>
-      </c>
-      <c r="F43" s="126">
+      <c r="D43" s="57"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="126" t="e">
         <f>D43/E43</f>
-        <v>1541.4673684210529</v>
-      </c>
-      <c r="G43" s="60">
-        <v>240</v>
-      </c>
-      <c r="H43" s="97">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G43" s="60"/>
+      <c r="H43" s="97" t="e">
         <f>F43*G43</f>
-        <v>369952.16842105269</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="I43" s="15"/>
       <c r="J43" s="15"/>
@@ -14225,8 +15514,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25ED0D34-371C-44C4-8709-6060745CC3BB}">
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A822D0D-B766-46D5-91D5-57B64E8762DA}">
   <dimension ref="B1:N56"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -14236,11 +15525,11 @@
     <col min="4" max="4" width="14" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.77734375" style="1" customWidth="1"/>
     <col min="10" max="10" width="8.33203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="40" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15.88671875" style="1" customWidth="1"/>
     <col min="14" max="14" width="22.5546875" style="1" customWidth="1"/>
@@ -14249,7 +15538,7 @@
   <sheetData>
     <row r="1" spans="2:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="186" t="s">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="C1" s="187"/>
       <c r="D1" s="187"/>
@@ -14258,16 +15547,14 @@
       <c r="G1" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="176">
-        <v>46243</v>
-      </c>
+      <c r="H1" s="176"/>
       <c r="I1" s="177"/>
       <c r="J1" s="17" t="s">
         <v>15</v>
       </c>
       <c r="K1" s="189">
         <f>M2-E2</f>
-        <v>-201485</v>
+        <v>0</v>
       </c>
       <c r="L1" s="190"/>
       <c r="M1" s="18"/>
@@ -14281,15 +15568,15 @@
       </c>
       <c r="E2" s="12">
         <f>SUM(E5:E30)</f>
-        <v>201485</v>
+        <v>0</v>
       </c>
       <c r="F2" s="20"/>
       <c r="G2" s="31" t="s">
         <v>32</v>
       </c>
       <c r="H2" s="178" t="str">
-        <f ca="1">IF(ISBLANK(H1),"0 Days",CONCATENATE(_xlfn.DAYS(TODAY(), H1)," days"))</f>
-        <v>39 days</v>
+        <f ca="1">IF(ISBLANK(H1),"0 Days",CONCATENATE(_xlfn.DAYS(TODAY()+1, H1)," days"))</f>
+        <v>0 Days</v>
       </c>
       <c r="I2" s="193"/>
       <c r="J2" s="37"/>
@@ -14369,18 +15656,10 @@
       <c r="B5" s="40">
         <v>1</v>
       </c>
-      <c r="C5" s="7">
-        <v>46243</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="9">
-        <v>165000</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>305</v>
-      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="23"/>
       <c r="G5" s="43"/>
       <c r="H5" s="44"/>
       <c r="I5" s="47" t="str">
@@ -14399,18 +15678,10 @@
       <c r="B6" s="40">
         <v>2</v>
       </c>
-      <c r="C6" s="7">
-        <v>46243</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" s="5">
-        <v>5000</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>306</v>
-      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="23"/>
       <c r="G6" s="43"/>
       <c r="H6" s="44"/>
       <c r="I6" s="47" t="str">
@@ -14420,7 +15691,7 @@
       <c r="J6" s="21">
         <v>2</v>
       </c>
-      <c r="K6" s="4"/>
+      <c r="K6" s="43"/>
       <c r="L6" s="3"/>
       <c r="M6" s="5"/>
       <c r="N6" s="22"/>
@@ -14429,15 +15700,9 @@
       <c r="B7" s="40">
         <v>3</v>
       </c>
-      <c r="C7" s="7">
-        <v>46249</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="5">
-        <v>16485</v>
-      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="5"/>
       <c r="F7" s="23"/>
       <c r="G7" s="43"/>
       <c r="H7" s="44"/>
@@ -14457,15 +15722,9 @@
       <c r="B8" s="40">
         <v>4</v>
       </c>
-      <c r="C8" s="7">
-        <v>46281</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="5">
-        <v>15000</v>
-      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="5"/>
       <c r="F8" s="22"/>
       <c r="G8" s="43"/>
       <c r="H8" s="44"/>
@@ -14485,7 +15744,7 @@
       <c r="B9" s="40">
         <v>5</v>
       </c>
-      <c r="C9" s="127"/>
+      <c r="C9" s="43"/>
       <c r="D9" s="3"/>
       <c r="E9" s="9"/>
       <c r="F9" s="22"/>
@@ -14623,9 +15882,7 @@
       <c r="G15" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="H15" s="176">
-        <v>46243</v>
-      </c>
+      <c r="H15" s="176"/>
       <c r="I15" s="177"/>
       <c r="J15" s="21">
         <v>11</v>
@@ -14647,8 +15904,8 @@
         <v>32</v>
       </c>
       <c r="H16" s="178" t="str">
-        <f ca="1">IF(ISBLANK(H15),"0 Days",CONCATENATE(_xlfn.DAYS(TODAY(), H1)," days"))</f>
-        <v>39 days</v>
+        <f ca="1">IF(ISBLANK(H15),"0 Days",CONCATENATE(_xlfn.DAYS(TODAY()+1, H1)," days"))</f>
+        <v>0 Days</v>
       </c>
       <c r="I16" s="179"/>
       <c r="J16" s="21">
@@ -15023,7 +16280,9 @@
       <c r="N33" s="15"/>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="E34" s="15"/>
+      <c r="E34" s="15" t="s">
+        <v>143</v>
+      </c>
       <c r="F34" s="57">
         <f t="shared" ref="F34:F39" si="2">H34*G34</f>
         <v>0</v>
@@ -15193,10 +16452,7 @@
         <v>200</v>
       </c>
       <c r="C43" s="172"/>
-      <c r="D43" s="57">
-        <f>F31-F40</f>
-        <v>550000</v>
-      </c>
+      <c r="D43" s="57"/>
       <c r="E43" s="15"/>
       <c r="F43" s="126" t="e">
         <f>D43/E43</f>
@@ -15258,17 +16514,17 @@
     <mergeCell ref="J41:K41"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="B44:C44"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
     <mergeCell ref="J38:K38"/>
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="J32:K32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
     <mergeCell ref="L32:M32"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="H1:I1"/>
@@ -15308,7 +16564,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E6D7927-4220-4E4C-ACDC-68E20558EC44}">
   <dimension ref="A1:V35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -15362,10 +16618,10 @@
         <v>19</v>
       </c>
       <c r="K1" s="168" t="s">
+        <v>296</v>
+      </c>
+      <c r="L1" s="168" t="s">
         <v>297</v>
-      </c>
-      <c r="L1" s="168" t="s">
-        <v>298</v>
       </c>
       <c r="M1" s="162"/>
       <c r="U1" s="112"/>
@@ -15992,30 +17248,29 @@
         <v>May2026 - July2026</v>
       </c>
       <c r="C15" s="144" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D15" s="145">
         <f t="shared" ref="D15" si="6">IF(F15="","",E15-F15)</f>
-        <v>-201485</v>
+        <v>110337</v>
       </c>
       <c r="E15" s="146">
         <f>'Term-14'!$M$2</f>
-        <v>0</v>
+        <v>761822</v>
       </c>
       <c r="F15" s="146">
         <f>'Term-14'!$E$2</f>
-        <v>201485</v>
+        <v>651485</v>
       </c>
       <c r="G15" s="147">
         <f>MIN('Term-14'!H6:H14)</f>
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="H15" s="148" t="str" cm="1">
-        <f t="array" aca="1" ref="H15:I15" ca="1">'Term-14'!H2:I2</f>
-        <v>39 days</v>
+        <f t="array" ref="H15:I15">'Term-14'!H2:I2</f>
+        <v>57 days</v>
       </c>
       <c r="I15" s="149">
-        <f ca="1"/>
         <v>0</v>
       </c>
       <c r="J15" s="150">
@@ -16024,11 +17279,11 @@
       </c>
       <c r="K15" s="150">
         <f>'Term-14'!$F$40</f>
-        <v>0</v>
+        <v>348842</v>
       </c>
       <c r="L15" s="151" t="str">
         <f>'Term-14'!$F$41</f>
-        <v>0%</v>
+        <v>63.43%</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
@@ -16174,15 +17429,15 @@
       <c r="C25" s="204"/>
       <c r="D25" s="9">
         <f>SUM(D2:D24)</f>
-        <v>4068767.4000000004</v>
+        <v>4380589.4000000004</v>
       </c>
       <c r="E25" s="87">
         <f>SUM(E2:E24)</f>
-        <v>21118306.399999999</v>
+        <v>21880128.399999999</v>
       </c>
       <c r="F25" s="87">
         <f>SUM(F2:F24)</f>
-        <v>17049539</v>
+        <v>17499539</v>
       </c>
       <c r="G25" s="136"/>
       <c r="H25" s="87"/>
@@ -16270,7 +17525,7 @@
       </c>
       <c r="D32" s="87">
         <f>SUM(D12:D15)</f>
-        <v>15677.899999999907</v>
+        <v>327499.89999999991</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -16304,10 +17559,11 @@
       </c>
       <c r="D35" s="9">
         <f>SUM(D29:D34)</f>
-        <v>4068767.4</v>
+        <v>4380589.4000000004</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B1:L1" xr:uid="{5E6D7927-4220-4E4C-ACDC-68E20558EC44}"/>
   <mergeCells count="1">
     <mergeCell ref="A25:C25"/>
   </mergeCells>
@@ -16316,7 +17572,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{433D1A15-D537-4C11-9349-148721BDD652}">
   <dimension ref="A1:N1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -16340,7 +17596,7 @@
       <c r="E1" s="206"/>
       <c r="F1" s="207" t="str">
         <f ca="1">DATEDIF(L1,TODAY(),"y")&amp;" year, "&amp;DATEDIF(L1,TODAY(),"ym")&amp;" months, "&amp;TODAY()-DATE(YEAR(TODAY()),MONTH(TODAY()),1)&amp;" days"</f>
-        <v>3 year, 5 months, 16 days</v>
+        <v>3 year, 5 months, 3 days</v>
       </c>
       <c r="G1" s="208"/>
       <c r="H1" s="208"/>
@@ -16365,7 +17621,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F397FBE2-11C6-4994-AF06-5D9D4133A216}">
   <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -16455,10 +17711,10 @@
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="86"/>
       <c r="B6" s="104" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C6" s="104" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D6" s="104"/>
       <c r="G6" s="113"/>
@@ -17378,7 +18634,7 @@
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F33" s="57">
         <f>H33*G33</f>
@@ -17542,6 +18798,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H13:I13"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -17550,35 +18812,29 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H13:I13"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D30">
-    <cfRule type="duplicateValues" dxfId="68" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E30">
-    <cfRule type="duplicateValues" dxfId="67" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" dxfId="66" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="72" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="71" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L30">
-    <cfRule type="duplicateValues" dxfId="64" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M30">
-    <cfRule type="duplicateValues" dxfId="63" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="S24:S26">
-    <cfRule type="duplicateValues" dxfId="62" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -18383,7 +19639,7 @@
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F33" s="57">
         <f>H33*G33</f>
@@ -18589,27 +19845,27 @@
     <mergeCell ref="G15:I15"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D30">
-    <cfRule type="duplicateValues" dxfId="61" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E30">
-    <cfRule type="duplicateValues" dxfId="60" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" dxfId="59" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="65" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="64" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L30">
-    <cfRule type="duplicateValues" dxfId="57" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M30">
-    <cfRule type="duplicateValues" dxfId="56" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="S24:S26">
-    <cfRule type="duplicateValues" dxfId="55" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -19453,7 +20709,7 @@
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F33" s="57">
         <f>H33*G33</f>
@@ -19525,7 +20781,7 @@
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.3">
       <c r="E36" s="15" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F36" s="57">
         <f t="shared" si="1"/>
@@ -19682,6 +20938,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="B3:F3"/>
@@ -19689,25 +20950,20 @@
     <mergeCell ref="J3:N3"/>
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="G14:I14"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" dxfId="54" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="60" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="59" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L22">
-    <cfRule type="duplicateValues" dxfId="52" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M22">
-    <cfRule type="duplicateValues" dxfId="51" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="21"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -20857,18 +22113,18 @@
     <mergeCell ref="G17:I17"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" dxfId="50" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="56" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="55" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L22">
-    <cfRule type="duplicateValues" dxfId="48" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M22">
-    <cfRule type="duplicateValues" dxfId="47" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -22172,11 +23428,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="A43:C43"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -22185,20 +23436,25 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" dxfId="46" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="52" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="51" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L22">
-    <cfRule type="duplicateValues" dxfId="44" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M22">
-    <cfRule type="duplicateValues" dxfId="43" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -23456,11 +24712,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -23469,23 +24720,28 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" dxfId="42" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="48" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5">
-    <cfRule type="duplicateValues" dxfId="40" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L6:L22">
-    <cfRule type="duplicateValues" dxfId="39" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M22">
-    <cfRule type="duplicateValues" dxfId="38" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -24627,6 +25883,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -24635,28 +25896,23 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" dxfId="37" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="43" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5">
-    <cfRule type="duplicateValues" dxfId="35" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L6:L22">
-    <cfRule type="duplicateValues" dxfId="34" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M22">
-    <cfRule type="duplicateValues" dxfId="33" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -25806,6 +27062,23 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -25814,40 +27087,23 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="B43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" dxfId="32" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5">
-    <cfRule type="duplicateValues" dxfId="30" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L6:L22">
-    <cfRule type="duplicateValues" dxfId="29" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M22">
-    <cfRule type="duplicateValues" dxfId="28" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15984FF0-8368-49C5-838D-A59A943FC5D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B45D98-8A74-498D-8E56-8552AB941609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="8" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="9" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Term-1" sheetId="4" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="320">
   <si>
     <t>#</t>
   </si>
@@ -1007,6 +1007,27 @@
   </si>
   <si>
     <t>Big Tank Loose Shell</t>
+  </si>
+  <si>
+    <t>Extra</t>
+  </si>
+  <si>
+    <t>Loose Shell</t>
+  </si>
+  <si>
+    <t>Last Term</t>
+  </si>
+  <si>
+    <t>4 tonea</t>
+  </si>
+  <si>
+    <t>From Ongole</t>
+  </si>
+  <si>
+    <t>Narisimha murthy</t>
+  </si>
+  <si>
+    <t>Term-15</t>
   </si>
 </sst>
 </file>
@@ -3145,9 +3166,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>List!$C$2:$C$15</c:f>
+              <c:f>List!$C$2:$C$16</c:f>
               <c:strCache>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>Term-1</c:v>
                 </c:pt>
@@ -3190,15 +3211,18 @@
                 <c:pt idx="13">
                   <c:v>Term-14</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>Term-15</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>List!$D$2:$D$15</c:f>
+              <c:f>List!$D$2:$D$16</c:f>
               <c:numCache>
                 <c:formatCode>"₹"\ #,##0</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>-790524</c:v>
                 </c:pt>
@@ -3239,7 +3263,10 @@
                   <c:v>76509.399999999907</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>110337</c:v>
+                  <c:v>22177</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-300000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3771,7 +3798,7 @@
                 <c:formatCode>"₹"\ #,##0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>4380589.4000000004</c:v>
+                  <c:v>3992429.4000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4186,7 +4213,7 @@
                   <c:v>3039754.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>327499.89999999991</c:v>
+                  <c:v>239339.89999999991</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14420,7 +14447,7 @@
       </c>
       <c r="K1" s="189">
         <f>M2-E2</f>
-        <v>110337</v>
+        <v>22177</v>
       </c>
       <c r="L1" s="190"/>
       <c r="M1" s="18"/>
@@ -14434,7 +14461,7 @@
       </c>
       <c r="E2" s="12">
         <f>SUM(E5:E30)</f>
-        <v>651485</v>
+        <v>781485</v>
       </c>
       <c r="F2" s="20"/>
       <c r="G2" s="31" t="s">
@@ -14451,7 +14478,7 @@
       </c>
       <c r="M2" s="12">
         <f>SUM(M5:M22)</f>
-        <v>761822</v>
+        <v>803662</v>
       </c>
       <c r="N2" s="20"/>
     </row>
@@ -14593,7 +14620,7 @@
         <v>143</v>
       </c>
       <c r="M6" s="5">
-        <v>65600</v>
+        <v>105600</v>
       </c>
       <c r="N6" s="22"/>
     </row>
@@ -14627,7 +14654,7 @@
         <v>312</v>
       </c>
       <c r="M7" s="5">
-        <v>2760</v>
+        <v>4600</v>
       </c>
       <c r="N7" s="22"/>
     </row>
@@ -14663,16 +14690,18 @@
       <c r="B9" s="40">
         <v>5</v>
       </c>
-      <c r="C9" s="43">
+      <c r="C9" s="7">
         <v>46299</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E9" s="9">
-        <v>450000</v>
-      </c>
-      <c r="F9" s="22"/>
+        <v>500000</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>316</v>
+      </c>
       <c r="G9" s="46"/>
       <c r="H9" s="44"/>
       <c r="I9" s="47" t="str">
@@ -14691,9 +14720,15 @@
       <c r="B10" s="40">
         <v>6</v>
       </c>
-      <c r="C10" s="127"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="9"/>
+      <c r="C10" s="7">
+        <v>46299</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="9">
+        <v>50000</v>
+      </c>
       <c r="F10" s="22"/>
       <c r="G10" s="46"/>
       <c r="H10" s="44"/>
@@ -14713,9 +14748,15 @@
       <c r="B11" s="40">
         <v>7</v>
       </c>
-      <c r="C11" s="127"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="5"/>
+      <c r="C11" s="7">
+        <v>46299</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E11" s="5">
+        <v>30000</v>
+      </c>
       <c r="F11" s="22"/>
       <c r="G11" s="46"/>
       <c r="H11" s="44"/>
@@ -14899,7 +14940,9 @@
       <c r="G19" s="43">
         <v>46299</v>
       </c>
-      <c r="H19" s="44"/>
+      <c r="H19" s="44">
+        <v>114</v>
+      </c>
       <c r="I19" s="47" t="str">
         <f>IF(ISBLANK(G19),"",CONCATENATE(G19-$H$15+1," days"))</f>
         <v>57 days</v>
@@ -15214,7 +15257,9 @@
       <c r="L33" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="M33" s="131"/>
+      <c r="M33" s="131">
+        <v>500000</v>
+      </c>
       <c r="N33" s="15"/>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.3">
@@ -15232,20 +15277,26 @@
         <v>400</v>
       </c>
       <c r="I34" s="60">
-        <v>164</v>
+        <v>264</v>
       </c>
       <c r="J34" s="169">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
-        <v>65600</v>
+        <v>105600</v>
       </c>
       <c r="K34" s="169"/>
-      <c r="L34" s="83"/>
-      <c r="M34" s="131"/>
+      <c r="L34" s="83" t="s">
+        <v>315</v>
+      </c>
+      <c r="M34" s="131">
+        <v>311458.09999999998</v>
+      </c>
       <c r="N34" s="15"/>
     </row>
     <row r="35" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C35" s="122"/>
-      <c r="E35" s="15"/>
+      <c r="E35" s="15" t="s">
+        <v>314</v>
+      </c>
       <c r="F35" s="57">
         <f t="shared" si="2"/>
         <v>5244</v>
@@ -15257,28 +15308,40 @@
         <v>46</v>
       </c>
       <c r="I35" s="60">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J35" s="169">
         <f t="shared" si="3"/>
-        <v>2760</v>
+        <v>4600</v>
       </c>
       <c r="K35" s="169"/>
-      <c r="L35" s="83"/>
-      <c r="M35" s="131"/>
+      <c r="L35" s="83" t="s">
+        <v>268</v>
+      </c>
+      <c r="M35" s="131">
+        <v>200000</v>
+      </c>
       <c r="N35" s="15" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="E36" s="15"/>
+      <c r="E36" s="15" t="s">
+        <v>313</v>
+      </c>
       <c r="F36" s="57">
         <f t="shared" si="2"/>
+        <v>1140</v>
+      </c>
+      <c r="G36" s="57">
+        <v>114</v>
+      </c>
+      <c r="H36" s="65">
+        <v>10</v>
+      </c>
+      <c r="I36" s="60">
         <v>0</v>
       </c>
-      <c r="G36" s="57"/>
-      <c r="H36" s="65"/>
-      <c r="I36" s="60"/>
       <c r="J36" s="169">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -15348,17 +15411,17 @@
       </c>
       <c r="F40" s="58">
         <f>SUM(F33:F38)</f>
-        <v>348842</v>
+        <v>349982</v>
       </c>
       <c r="G40" s="58"/>
       <c r="H40" s="82">
         <f>SUM(H33:H39)</f>
-        <v>3053</v>
+        <v>3063</v>
       </c>
       <c r="I40" s="50"/>
       <c r="J40" s="170">
         <f>SUM(J33:J39)</f>
-        <v>761822</v>
+        <v>803662</v>
       </c>
       <c r="K40" s="170"/>
       <c r="L40" s="50" t="s">
@@ -15366,7 +15429,7 @@
       </c>
       <c r="M40" s="132">
         <f>SUM(M33:M39)</f>
-        <v>0</v>
+        <v>1011458.1</v>
       </c>
       <c r="N40" s="15"/>
     </row>
@@ -15376,7 +15439,7 @@
       </c>
       <c r="F41" s="105" t="str">
         <f>CONCATENATE(ROUND((F40/F31)*100,2),"%")</f>
-        <v>63.43%</v>
+        <v>63.63%</v>
       </c>
       <c r="G41" s="15"/>
       <c r="H41" s="56"/>
@@ -15388,7 +15451,7 @@
       </c>
       <c r="M41" s="101">
         <f>J40-M40</f>
-        <v>761822</v>
+        <v>-207796.09999999998</v>
       </c>
       <c r="N41" s="15"/>
     </row>
@@ -15547,14 +15610,16 @@
       <c r="G1" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="176"/>
+      <c r="H1" s="176">
+        <v>46316</v>
+      </c>
       <c r="I1" s="177"/>
       <c r="J1" s="17" t="s">
         <v>15</v>
       </c>
       <c r="K1" s="189">
         <f>M2-E2</f>
-        <v>0</v>
+        <v>-300000</v>
       </c>
       <c r="L1" s="190"/>
       <c r="M1" s="18"/>
@@ -15568,7 +15633,7 @@
       </c>
       <c r="E2" s="12">
         <f>SUM(E5:E30)</f>
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="F2" s="20"/>
       <c r="G2" s="31" t="s">
@@ -15576,7 +15641,7 @@
       </c>
       <c r="H2" s="178" t="str">
         <f ca="1">IF(ISBLANK(H1),"0 Days",CONCATENATE(_xlfn.DAYS(TODAY()+1, H1)," days"))</f>
-        <v>0 Days</v>
+        <v>0 days</v>
       </c>
       <c r="I2" s="193"/>
       <c r="J2" s="37"/>
@@ -15656,10 +15721,18 @@
       <c r="B5" s="40">
         <v>1</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="23"/>
+      <c r="C5" s="7">
+        <v>46316</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="9">
+        <v>280000</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>317</v>
+      </c>
       <c r="G5" s="43"/>
       <c r="H5" s="44"/>
       <c r="I5" s="47" t="str">
@@ -15678,10 +15751,18 @@
       <c r="B6" s="40">
         <v>2</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="23"/>
+      <c r="C6" s="7">
+        <v>46316</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E6" s="5">
+        <v>20000</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>318</v>
+      </c>
       <c r="G6" s="43"/>
       <c r="H6" s="44"/>
       <c r="I6" s="47" t="str">
@@ -15882,7 +15963,9 @@
       <c r="G15" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="H15" s="176"/>
+      <c r="H15" s="176">
+        <v>46316</v>
+      </c>
       <c r="I15" s="177"/>
       <c r="J15" s="21">
         <v>11</v>
@@ -15905,7 +15988,7 @@
       </c>
       <c r="H16" s="178" t="str">
         <f ca="1">IF(ISBLANK(H15),"0 Days",CONCATENATE(_xlfn.DAYS(TODAY()+1, H1)," days"))</f>
-        <v>0 Days</v>
+        <v>0 days</v>
       </c>
       <c r="I16" s="179"/>
       <c r="J16" s="21">
@@ -16216,20 +16299,16 @@
       </c>
       <c r="F31" s="84">
         <f>H31+J31</f>
-        <v>550000</v>
+        <v>0</v>
       </c>
       <c r="G31" s="90" t="s">
         <v>186</v>
       </c>
-      <c r="H31" s="84">
-        <v>450000</v>
-      </c>
+      <c r="H31" s="84"/>
       <c r="I31" s="59" t="s">
         <v>187</v>
       </c>
-      <c r="J31" s="84">
-        <v>100000</v>
-      </c>
+      <c r="J31" s="84"/>
       <c r="K31" s="84"/>
       <c r="L31" s="96"/>
       <c r="M31" s="130"/>
@@ -16280,9 +16359,7 @@
       <c r="N33" s="15"/>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="E34" s="15" t="s">
-        <v>143</v>
-      </c>
+      <c r="E34" s="15"/>
       <c r="F34" s="57">
         <f t="shared" ref="F34:F39" si="2">H34*G34</f>
         <v>0</v>
@@ -16424,9 +16501,9 @@
       <c r="E41" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="F41" s="105" t="str">
+      <c r="F41" s="105" t="e">
         <f>CONCATENATE(ROUND((F40/F31)*100,2),"%")</f>
-        <v>0%</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G41" s="15"/>
       <c r="H41" s="56"/>
@@ -16514,17 +16591,17 @@
     <mergeCell ref="J41:K41"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="B44:C44"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
     <mergeCell ref="J38:K38"/>
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="J32:K32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
     <mergeCell ref="L32:M32"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="H1:I1"/>
@@ -17244,23 +17321,23 @@
         <v>14</v>
       </c>
       <c r="B15" s="143" t="str">
-        <f>'Term-13'!$B$1</f>
-        <v>May2026 - July2026</v>
+        <f>'Term-14'!$B$1</f>
+        <v>Aug2026 - Sept2026</v>
       </c>
       <c r="C15" s="144" t="s">
         <v>291</v>
       </c>
       <c r="D15" s="145">
         <f t="shared" ref="D15" si="6">IF(F15="","",E15-F15)</f>
-        <v>110337</v>
+        <v>22177</v>
       </c>
       <c r="E15" s="146">
         <f>'Term-14'!$M$2</f>
-        <v>761822</v>
+        <v>803662</v>
       </c>
       <c r="F15" s="146">
         <f>'Term-14'!$E$2</f>
-        <v>651485</v>
+        <v>781485</v>
       </c>
       <c r="G15" s="147">
         <f>MIN('Term-14'!H6:H14)</f>
@@ -17279,27 +17356,59 @@
       </c>
       <c r="K15" s="150">
         <f>'Term-14'!$F$40</f>
-        <v>348842</v>
+        <v>349982</v>
       </c>
       <c r="L15" s="151" t="str">
         <f>'Term-14'!$F$41</f>
-        <v>63.43%</v>
+        <v>63.63%</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" s="86">
         <v>15</v>
       </c>
-      <c r="B16" s="123"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="93"/>
-      <c r="E16" s="87"/>
-      <c r="F16" s="87"/>
-      <c r="G16" s="136"/>
-      <c r="H16" s="135"/>
-      <c r="J16" s="140"/>
-      <c r="K16" s="104"/>
-      <c r="L16" s="141"/>
+      <c r="B16" s="143" t="str">
+        <f>'Term-15'!$B$1</f>
+        <v>Oct2026 - Dec2026</v>
+      </c>
+      <c r="C16" s="144" t="s">
+        <v>319</v>
+      </c>
+      <c r="D16" s="145">
+        <f t="shared" ref="D16" si="7">IF(F16="","",E16-F16)</f>
+        <v>-300000</v>
+      </c>
+      <c r="E16" s="146">
+        <f>'Term-15'!$M$2</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="146">
+        <f>'Term-15'!$E$2</f>
+        <v>300000</v>
+      </c>
+      <c r="G16" s="147">
+        <f>MIN('Term-15'!H6:H14)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="148" cm="1">
+        <f t="array" ref="H16:I16">'Term-15'!H3:I3</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="149">
+        <v>0</v>
+      </c>
+      <c r="J16" s="150">
+        <f>'Term-15'!$F$31</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="150">
+        <f>'Term-15'!$F$40</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="151" t="e">
+        <f>'Term-15'!$F$41</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="86">
@@ -17429,15 +17538,15 @@
       <c r="C25" s="204"/>
       <c r="D25" s="9">
         <f>SUM(D2:D24)</f>
-        <v>4380589.4000000004</v>
+        <v>3992429.4000000004</v>
       </c>
       <c r="E25" s="87">
         <f>SUM(E2:E24)</f>
-        <v>21880128.399999999</v>
+        <v>21921968.399999999</v>
       </c>
       <c r="F25" s="87">
         <f>SUM(F2:F24)</f>
-        <v>17499539</v>
+        <v>17929539</v>
       </c>
       <c r="G25" s="136"/>
       <c r="H25" s="87"/>
@@ -17521,11 +17630,11 @@
       </c>
       <c r="C32" s="104">
         <f>COUNTIF(C13:C16, "*")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D32" s="87">
         <f>SUM(D12:D15)</f>
-        <v>327499.89999999991</v>
+        <v>239339.89999999991</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -17555,11 +17664,11 @@
       </c>
       <c r="C35" s="8">
         <f>SUM(C29:C34)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D35" s="9">
         <f>SUM(D29:D34)</f>
-        <v>4380589.4000000004</v>
+        <v>4292429.4000000004</v>
       </c>
     </row>
   </sheetData>
@@ -17596,7 +17705,7 @@
       <c r="E1" s="206"/>
       <c r="F1" s="207" t="str">
         <f ca="1">DATEDIF(L1,TODAY(),"y")&amp;" year, "&amp;DATEDIF(L1,TODAY(),"ym")&amp;" months, "&amp;TODAY()-DATE(YEAR(TODAY()),MONTH(TODAY()),1)&amp;" days"</f>
-        <v>3 year, 5 months, 3 days</v>
+        <v>3 year, 6 months, 19 days</v>
       </c>
       <c r="G1" s="208"/>
       <c r="H1" s="208"/>
